--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -45,9 +45,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F4E78"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,34 +78,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -188,18 +173,1502 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DebtSustainabilityTable" displayName="DebtSustainabilityTable" ref="A1:E4" headerRowCount="1">
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_CreditPosition" displayName="T_CreditPosition" ref="A1:V4" headerRowCount="1">
+  <autoFilter ref="A1:V4"/>
+  <tableColumns count="22">
+    <tableColumn id="1" name="position_id"/>
+    <tableColumn id="2" name="revenue"/>
+    <tableColumn id="3" name="change_in_finished_goods_inventory"/>
+    <tableColumn id="4" name="operating_grants"/>
+    <tableColumn id="5" name="net_purchases"/>
+    <tableColumn id="6" name="change_in_raw_materials_inventory"/>
+    <tableColumn id="7" name="costs_for_services_and_third_party_assets"/>
+    <tableColumn id="8" name="personnel_costs"/>
+    <tableColumn id="9" name="depreciation_tangible_assets"/>
+    <tableColumn id="10" name="working_capital_impairments"/>
+    <tableColumn id="11" name="operating_provisions"/>
+    <tableColumn id="12" name="other_income_expenses_balance"/>
+    <tableColumn id="13" name="operating_value_added"/>
+    <tableColumn id="14" name="gross_operating_margin"/>
+    <tableColumn id="15" name="net_operating_margin"/>
+    <tableColumn id="16" name="ebitda"/>
+    <tableColumn id="17" name="profit_loss"/>
+    <tableColumn id="18" name="ebitda_margin"/>
+    <tableColumn id="19" name="ebitda_inventory_contribution"/>
+    <tableColumn id="20" name="nfp_to_ebitda"/>
+    <tableColumn id="21" name="interest_expense"/>
+    <tableColumn id="22" name="revenue_growth"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_CustomerProfile" displayName="T_CustomerProfile" ref="A1:AP4" headerRowCount="1">
+  <autoFilter ref="A1:AP4"/>
+  <tableColumns count="42">
+    <tableColumn id="1" name="position_id"/>
+    <tableColumn id="2" name="company_name"/>
+    <tableColumn id="3" name="counterparty_type"/>
+    <tableColumn id="4" name="legal_form"/>
+    <tableColumn id="5" name="sector"/>
+    <tableColumn id="6" name="size_class"/>
+    <tableColumn id="7" name="geography"/>
+    <tableColumn id="8" name="business_history_years"/>
+    <tableColumn id="9" name="operations"/>
+    <tableColumn id="10" name="minimum_regulatory_risk_grade"/>
+    <tableColumn id="11" name="previous_risk_grade"/>
+    <tableColumn id="12" name="risk_grade_change"/>
+    <tableColumn id="13" name="past_due_count"/>
+    <tableColumn id="14" name="cure_period_days"/>
+    <tableColumn id="15" name="monitoring_period_days"/>
+    <tableColumn id="16" name="probation_period_days"/>
+    <tableColumn id="17" name="forborne_non_performing_exit"/>
+    <tableColumn id="18" name="ews_score_class"/>
+    <tableColumn id="19" name="ews_score_notching"/>
+    <tableColumn id="20" name="ews_score_variation"/>
+    <tableColumn id="21" name="active_ewis"/>
+    <tableColumn id="22" name="rating"/>
+    <tableColumn id="23" name="rating_notching"/>
+    <tableColumn id="24" name="rating_influential_factors"/>
+    <tableColumn id="25" name="rating_elementary_modules"/>
+    <tableColumn id="26" name="pd"/>
+    <tableColumn id="27" name="risk_group_interdependence"/>
+    <tableColumn id="28" name="risk_group_independence"/>
+    <tableColumn id="29" name="shareholders"/>
+    <tableColumn id="30" name="shareholder_roles"/>
+    <tableColumn id="31" name="management_members"/>
+    <tableColumn id="32" name="generational_transition"/>
+    <tableColumn id="33" name="employment_contract_type"/>
+    <tableColumn id="34" name="economic_family_context"/>
+    <tableColumn id="35" name="relationship_years"/>
+    <tableColumn id="36" name="historical_facilities"/>
+    <tableColumn id="37" name="previous_restructuring"/>
+    <tableColumn id="38" name="forborne"/>
+    <tableColumn id="39" name="protests"/>
+    <tableColumn id="40" name="bankruptcies"/>
+    <tableColumn id="41" name="litigation"/>
+    <tableColumn id="42" name="significant_historical_events"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_Behavioural" displayName="T_Behavioural" ref="A1:E4" headerRowCount="1">
   <autoFilter ref="A1:E4"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="scenario_id"/>
+    <tableColumn id="1" name="position_id"/>
+    <tableColumn id="2" name="average_utilization"/>
+    <tableColumn id="3" name="overdraft_days"/>
+    <tableColumn id="4" name="payment_delay_days"/>
+    <tableColumn id="5" name="exposure_growth"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_DebtSustainability" displayName="T_DebtSustainability" ref="A1:E4" headerRowCount="1">
+  <autoFilter ref="A1:E4"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="position_id"/>
     <tableColumn id="2" name="cash_flow_available_for_debt_service"/>
     <tableColumn id="3" name="debt_service"/>
     <tableColumn id="4" name="ebitda"/>
     <tableColumn id="5" name="interest_expense"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Excel Demo Scenarios — Credit Assessment System</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Synthetic workbook for demonstrating the Excel input mode of the credit assessment system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Scenarios</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-NORMAL, DEMO-ATTENTION, DEMO-CRITICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Deterministic engine</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Scenario data are evaluated by the deterministic rule engine; LLM components only support comments/reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>No material financial or behavioural triggers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ATTENTION</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>One medium-severity financial trigger (revenue growth = -15%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Multiple high-severity financial triggers, including revenue deterioration, leverage and interest burden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Workbook contract</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Credit_Position is required. Customer_Profile, Behavioural and Debt_Sustainability are optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>List convention</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Multi-value fields use semicolon-separated values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Boolean convention</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Use TRUE/FALSE values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>All values are synthetic and contain no confidential banking information.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>position_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>change_in_finished_goods_inventory</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>operating_grants</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>net_purchases</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>change_in_raw_materials_inventory</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>costs_for_services_and_third_party_assets</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>personnel_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>depreciation_tangible_assets</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>working_capital_impairments</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>operating_provisions</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>other_income_expenses_balance</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>operating_value_added</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>gross_operating_margin</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>net_operating_margin</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>profit_loss</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>ebitda_margin</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>ebitda_inventory_contribution</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>nfp_to_ebitda</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>revenue_growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-NORMAL</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="O2" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-ATTENTION</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="O3" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-CRITICAL</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>300000</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:V4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AP4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="18" customWidth="1" min="41" max="41"/>
+    <col width="30" customWidth="1" min="42" max="42"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>position_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>counterparty_type</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>legal_form</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>size_class</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>business_history_years</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>minimum_regulatory_risk_grade</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>previous_risk_grade</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>risk_grade_change</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>past_due_count</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>cure_period_days</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>monitoring_period_days</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>probation_period_days</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>forborne_non_performing_exit</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>ews_score_class</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>ews_score_notching</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>ews_score_variation</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>active_ewis</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="W1" s="5" t="inlineStr">
+        <is>
+          <t>rating_notching</t>
+        </is>
+      </c>
+      <c r="X1" s="5" t="inlineStr">
+        <is>
+          <t>rating_influential_factors</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>rating_elementary_modules</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>pd</t>
+        </is>
+      </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>risk_group_interdependence</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>risk_group_independence</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>shareholders</t>
+        </is>
+      </c>
+      <c r="AD1" s="5" t="inlineStr">
+        <is>
+          <t>shareholder_roles</t>
+        </is>
+      </c>
+      <c r="AE1" s="5" t="inlineStr">
+        <is>
+          <t>management_members</t>
+        </is>
+      </c>
+      <c r="AF1" s="5" t="inlineStr">
+        <is>
+          <t>generational_transition</t>
+        </is>
+      </c>
+      <c r="AG1" s="5" t="inlineStr">
+        <is>
+          <t>employment_contract_type</t>
+        </is>
+      </c>
+      <c r="AH1" s="5" t="inlineStr">
+        <is>
+          <t>economic_family_context</t>
+        </is>
+      </c>
+      <c r="AI1" s="5" t="inlineStr">
+        <is>
+          <t>relationship_years</t>
+        </is>
+      </c>
+      <c r="AJ1" s="5" t="inlineStr">
+        <is>
+          <t>historical_facilities</t>
+        </is>
+      </c>
+      <c r="AK1" s="5" t="inlineStr">
+        <is>
+          <t>previous_restructuring</t>
+        </is>
+      </c>
+      <c r="AL1" s="5" t="inlineStr">
+        <is>
+          <t>forborne</t>
+        </is>
+      </c>
+      <c r="AM1" s="5" t="inlineStr">
+        <is>
+          <t>protests</t>
+        </is>
+      </c>
+      <c r="AN1" s="5" t="inlineStr">
+        <is>
+          <t>bankruptcies</t>
+        </is>
+      </c>
+      <c r="AO1" s="5" t="inlineStr">
+        <is>
+          <t>litigation</t>
+        </is>
+      </c>
+      <c r="AP1" s="5" t="inlineStr">
+        <is>
+          <t>significant_historical_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-NORMAL</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Alpha Industrial S.p.A.</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>S.p.A.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Mid-cap</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Lombardy</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing operations</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Bonis</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Bonis</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>Stable financial profile</t>
+        </is>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>Financial statements</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AA2" s="4" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="AB2" s="4" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Family shareholders</t>
+        </is>
+      </c>
+      <c r="AD2" s="4" t="inlineStr">
+        <is>
+          <t>Shareholders</t>
+        </is>
+      </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>Management team</t>
+        </is>
+      </c>
+      <c r="AF2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="4" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="AH2" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>Loans; Credit lines</t>
+        </is>
+      </c>
+      <c r="AK2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="4" t="inlineStr"/>
+      <c r="AN2" s="4" t="inlineStr"/>
+      <c r="AO2" s="4" t="inlineStr"/>
+      <c r="AP2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-ATTENTION</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Beta Industrial S.p.A.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>S.p.A.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Mid-cap</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Lombardy</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing operations</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Bonis</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Bonis</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>Stable financial profile</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>Financial statements</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Family shareholders</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>Shareholders</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>Management team</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>Loans; Credit lines</t>
+        </is>
+      </c>
+      <c r="AK3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4" t="inlineStr"/>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr"/>
+      <c r="AP3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-CRITICAL</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Gamma Industrial S.p.A.</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>S.p.A.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Mid-cap</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Lombardy</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Manufacturing operations</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Bonis</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Bonis</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Stable financial profile</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>Financial statements</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Family shareholders</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>Shareholders</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>Management team</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>Loans; Credit lines</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="4" t="inlineStr"/>
+      <c r="AN4" s="4" t="inlineStr"/>
+      <c r="AO4" s="4" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AP4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>position_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>average_utilization</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>overdraft_days</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>payment_delay_days</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>exposure_growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-NORMAL</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-ATTENTION</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DEMO-CRITICAL</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -211,42 +1680,42 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>scenario_id</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>position_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>cash_flow_available_for_debt_service</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>debt_service</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>DEMO-NORMAL</t>
         </is>
@@ -258,14 +1727,14 @@
         <v>600000</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>200000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>DEMO-ATTENTION</t>
         </is>
@@ -277,23 +1746,23 @@
         <v>600000</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>200000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>DEMO-CRITICAL</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>600000</v>
+        <v>900000</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1000000</v>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4B86016-888E-48B7-8226-148D1E7FF37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4B1FB0-1C3B-427F-A2F5-02A860360387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Debt_Sustainability!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -96,9 +95,6 @@
     <t>All values are synthetic and contain no confidential banking information.</t>
   </si>
   <si>
-    <t>position_id</t>
-  </si>
-  <si>
     <t>revenue</t>
   </si>
   <si>
@@ -373,6 +369,9 @@
   </si>
   <si>
     <t>debt_service</t>
+  </si>
+  <si>
+    <t>scenario_id</t>
   </si>
 </sst>
 </file>
@@ -902,81 +901,81 @@
   <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
     <col min="2" max="22" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4">
         <v>10000000</v>
@@ -1044,7 +1043,7 @@
     </row>
     <row r="3" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>10000000</v>
@@ -1112,7 +1111,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>10000000</v>
@@ -1230,186 +1229,186 @@
   <sheetData>
     <row r="1" spans="1:42" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="AP1" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="H2" s="2">
         <v>12</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="S2" s="2">
         <v>0</v>
@@ -1419,49 +1418,49 @@
       </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="W2" s="2">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="Z2" s="2">
         <v>0.01</v>
       </c>
       <c r="AA2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AB2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AF2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="AH2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI2" s="2">
         <v>8</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK2" s="2" t="b">
         <v>0</v>
@@ -1476,58 +1475,58 @@
     </row>
     <row r="3" spans="1:42" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="H3" s="2">
         <v>12</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
@@ -1537,49 +1536,49 @@
       </c>
       <c r="U3" s="2"/>
       <c r="V3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="W3" s="2">
-        <v>0</v>
-      </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="Z3" s="2">
         <v>0.01</v>
       </c>
       <c r="AA3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AB3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AF3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AF3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="AH3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI3" s="2">
         <v>8</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK3" s="2" t="b">
         <v>0</v>
@@ -1594,58 +1593,58 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="H4" s="2">
         <v>12</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="S4" s="2">
         <v>0</v>
@@ -1655,49 +1654,49 @@
       </c>
       <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="2">
-        <v>0</v>
-      </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="Z4" s="2">
         <v>0.01</v>
       </c>
       <c r="AA4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AB4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC4" s="2" t="s">
+      <c r="AD4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AD4" s="2" t="s">
+      <c r="AE4" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AE4" s="2" t="s">
+      <c r="AF4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AF4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="AH4" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI4" s="2">
         <v>8</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK4" s="2" t="b">
         <v>0</v>
@@ -1733,24 +1732,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="5">
         <v>0.5</v>
@@ -1767,7 +1766,7 @@
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="5">
         <v>0.5</v>
@@ -1784,7 +1783,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5">
         <v>0.5</v>
@@ -1822,24 +1821,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4">
         <v>1500000</v>
@@ -1856,7 +1855,7 @@
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>1500000</v>
@@ -1873,7 +1872,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>800000</v>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BABFFD3C-519C-405B-AD15-F75AF5F57DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D61D857-D16C-48DF-9DE9-6E87E719D52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Credit_Position" sheetId="2" r:id="rId2"/>
-    <sheet name="Customer_Profile" sheetId="3" r:id="rId3"/>
-    <sheet name="Behavioural" sheetId="4" r:id="rId4"/>
-    <sheet name="Debt_Sustainability" sheetId="5" r:id="rId5"/>
+    <sheet name="Customer Profile" sheetId="2" r:id="rId2"/>
+    <sheet name="Financial Analysis" sheetId="3" r:id="rId3"/>
+    <sheet name="Behavioural Analysis" sheetId="4" r:id="rId4"/>
+    <sheet name="Debt Sustainability" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Behavioural!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Credit_Position!$A$1:$V$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Customer_Profile!$A$1:$AP$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Debt_Sustainability!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Behavioural Analysis'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer Profile'!$A$1:$AP$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Debt Sustainability'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Financial Analysis'!$A$1:$V$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="123">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -66,25 +66,25 @@
     <t>Sheet</t>
   </si>
   <si>
-    <t>Credit_Position</t>
+    <t>Financial Analysis</t>
   </si>
   <si>
     <t>Financial and accounting inputs used by the deterministic financial rules.</t>
   </si>
   <si>
-    <t>Customer_Profile</t>
+    <t>Customer Profile</t>
   </si>
   <si>
     <t>Customer context, risk profile, relationship and relevant credit-history events.</t>
   </si>
   <si>
-    <t>Behavioural</t>
+    <t>Behavioural Analysis</t>
   </si>
   <si>
     <t>Banking-behaviour inputs used by behavioural assessment rules.</t>
   </si>
   <si>
-    <t>Debt_Sustainability</t>
+    <t>Debt Sustainability</t>
   </si>
   <si>
     <t>Inputs used for debt-service and repayment-capacity assessment.</t>
@@ -126,6 +126,198 @@
     <t>scenario_id</t>
   </si>
   <si>
+    <t>company_name</t>
+  </si>
+  <si>
+    <t>counterparty_type</t>
+  </si>
+  <si>
+    <t>legal_form</t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>size_class</t>
+  </si>
+  <si>
+    <t>geography</t>
+  </si>
+  <si>
+    <t>business_history_years</t>
+  </si>
+  <si>
+    <t>operations</t>
+  </si>
+  <si>
+    <t>forborne_non_performing_exit</t>
+  </si>
+  <si>
+    <t>past_due_count</t>
+  </si>
+  <si>
+    <t>cure_period_days</t>
+  </si>
+  <si>
+    <t>monitoring_period_days</t>
+  </si>
+  <si>
+    <t>probation_period_days</t>
+  </si>
+  <si>
+    <t>minimum_regulatory_risk_grade</t>
+  </si>
+  <si>
+    <t>previous_risk_grade</t>
+  </si>
+  <si>
+    <t>risk_grade_change</t>
+  </si>
+  <si>
+    <t>ews_score_class</t>
+  </si>
+  <si>
+    <t>ews_score_notching</t>
+  </si>
+  <si>
+    <t>ews_score_variation</t>
+  </si>
+  <si>
+    <t>active_ewis</t>
+  </si>
+  <si>
+    <t>rating</t>
+  </si>
+  <si>
+    <t>rating_notching</t>
+  </si>
+  <si>
+    <t>rating_influential_factors</t>
+  </si>
+  <si>
+    <t>rating_elementary_modules</t>
+  </si>
+  <si>
+    <t>pd</t>
+  </si>
+  <si>
+    <t>risk_group_interdependence</t>
+  </si>
+  <si>
+    <t>risk_group_independence</t>
+  </si>
+  <si>
+    <t>shareholders</t>
+  </si>
+  <si>
+    <t>shareholder_roles</t>
+  </si>
+  <si>
+    <t>management_members</t>
+  </si>
+  <si>
+    <t>generational_transition</t>
+  </si>
+  <si>
+    <t>employment_contract_type</t>
+  </si>
+  <si>
+    <t>economic_family_context</t>
+  </si>
+  <si>
+    <t>relationship_years</t>
+  </si>
+  <si>
+    <t>historical_facilities</t>
+  </si>
+  <si>
+    <t>previous_restructuring</t>
+  </si>
+  <si>
+    <t>forborne</t>
+  </si>
+  <si>
+    <t>protests</t>
+  </si>
+  <si>
+    <t>bankruptcies</t>
+  </si>
+  <si>
+    <t>litigation</t>
+  </si>
+  <si>
+    <t>significant_historical_events</t>
+  </si>
+  <si>
+    <t>S.p.A.</t>
+  </si>
+  <si>
+    <t>Industrial manufacturing</t>
+  </si>
+  <si>
+    <t>Mid-cap</t>
+  </si>
+  <si>
+    <t>Northern Italy</t>
+  </si>
+  <si>
+    <t>Industrial manufacturing;B2B equipment supply</t>
+  </si>
+  <si>
+    <t>Past Due</t>
+  </si>
+  <si>
+    <t>Bonis</t>
+  </si>
+  <si>
+    <t>Bonis → Past Due</t>
+  </si>
+  <si>
+    <t>LIGHT_RED</t>
+  </si>
+  <si>
+    <t>Downward notching</t>
+  </si>
+  <si>
+    <t>Revenue deterioration;High credit utilization;Payment delay</t>
+  </si>
+  <si>
+    <t>BB-</t>
+  </si>
+  <si>
+    <t>Downward notching due to financial deterioration</t>
+  </si>
+  <si>
+    <t>Leverage;Liquidity;Profitability</t>
+  </si>
+  <si>
+    <t>Financial profile;Behavioural profile</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Family holding;Management shareholders</t>
+  </si>
+  <si>
+    <t>Controlling shareholder;Executive shareholder</t>
+  </si>
+  <si>
+    <t>CEO;CFO</t>
+  </si>
+  <si>
+    <t>Revolving credit;Term loan</t>
+  </si>
+  <si>
+    <t>Commercial dispute - ongoing</t>
+  </si>
+  <si>
+    <t>Ownership restructuring in 2024</t>
+  </si>
+  <si>
     <t>revenue</t>
   </si>
   <si>
@@ -189,196 +381,7 @@
     <t>revenue_growth</t>
   </si>
   <si>
-    <t>company_name</t>
-  </si>
-  <si>
-    <t>counterparty_type</t>
-  </si>
-  <si>
-    <t>legal_form</t>
-  </si>
-  <si>
-    <t>sector</t>
-  </si>
-  <si>
-    <t>size_class</t>
-  </si>
-  <si>
-    <t>geography</t>
-  </si>
-  <si>
-    <t>business_history_years</t>
-  </si>
-  <si>
-    <t>operations</t>
-  </si>
-  <si>
-    <t>forborne_non_performing_exit</t>
-  </si>
-  <si>
-    <t>past_due_count</t>
-  </si>
-  <si>
-    <t>cure_period_days</t>
-  </si>
-  <si>
-    <t>monitoring_period_days</t>
-  </si>
-  <si>
-    <t>probation_period_days</t>
-  </si>
-  <si>
-    <t>minimum_regulatory_risk_grade</t>
-  </si>
-  <si>
-    <t>previous_risk_grade</t>
-  </si>
-  <si>
-    <t>risk_grade_change</t>
-  </si>
-  <si>
-    <t>ews_score_class</t>
-  </si>
-  <si>
-    <t>ews_score_notching</t>
-  </si>
-  <si>
-    <t>ews_score_variation</t>
-  </si>
-  <si>
-    <t>active_ewis</t>
-  </si>
-  <si>
-    <t>rating</t>
-  </si>
-  <si>
-    <t>rating_notching</t>
-  </si>
-  <si>
-    <t>rating_influential_factors</t>
-  </si>
-  <si>
-    <t>rating_elementary_modules</t>
-  </si>
-  <si>
-    <t>pd</t>
-  </si>
-  <si>
-    <t>risk_group_interdependence</t>
-  </si>
-  <si>
-    <t>risk_group_independence</t>
-  </si>
-  <si>
-    <t>shareholders</t>
-  </si>
-  <si>
-    <t>shareholder_roles</t>
-  </si>
-  <si>
-    <t>management_members</t>
-  </si>
-  <si>
-    <t>generational_transition</t>
-  </si>
-  <si>
-    <t>employment_contract_type</t>
-  </si>
-  <si>
-    <t>economic_family_context</t>
-  </si>
-  <si>
-    <t>relationship_years</t>
-  </si>
-  <si>
-    <t>historical_facilities</t>
-  </si>
-  <si>
-    <t>previous_restructuring</t>
-  </si>
-  <si>
-    <t>forborne</t>
-  </si>
-  <si>
-    <t>protests</t>
-  </si>
-  <si>
-    <t>bankruptcies</t>
-  </si>
-  <si>
-    <t>litigation</t>
-  </si>
-  <si>
-    <t>significant_historical_events</t>
-  </si>
-  <si>
-    <t>S.p.A.</t>
-  </si>
-  <si>
-    <t>Industrial manufacturing</t>
-  </si>
-  <si>
-    <t>Mid-cap</t>
-  </si>
-  <si>
-    <t>Northern Italy</t>
-  </si>
-  <si>
-    <t>Industrial manufacturing;B2B equipment supply</t>
-  </si>
-  <si>
-    <t>Past Due</t>
-  </si>
-  <si>
-    <t>Bonis</t>
-  </si>
-  <si>
-    <t>Bonis → Past Due</t>
-  </si>
-  <si>
-    <t>LIGHT_RED</t>
-  </si>
-  <si>
-    <t>Downward notching</t>
-  </si>
-  <si>
-    <t>Revenue deterioration;High credit utilization;Payment delay</t>
-  </si>
-  <si>
-    <t>BB-</t>
-  </si>
-  <si>
-    <t>Downward notching due to financial deterioration</t>
-  </si>
-  <si>
-    <t>Leverage;Liquidity;Profitability</t>
-  </si>
-  <si>
-    <t>Financial profile;Behavioural profile</t>
-  </si>
-  <si>
-    <t>Moderate</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Family holding;Management shareholders</t>
-  </si>
-  <si>
-    <t>Controlling shareholder;Executive shareholder</t>
-  </si>
-  <si>
-    <t>CEO;CFO</t>
-  </si>
-  <si>
-    <t>Revolving credit;Term loan</t>
-  </si>
-  <si>
-    <t>Commercial dispute - ongoing</t>
-  </si>
-  <si>
-    <t>Ownership restructuring in 2024</t>
+    <t>contribution_margin</t>
   </si>
   <si>
     <t>average_utilization</t>
@@ -452,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -464,6 +467,19 @@
       <left style="thin">
         <color rgb="FFD9E1F2"/>
       </left>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E1F2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFD9E1F2"/>
       </right>
@@ -502,9 +518,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -965,177 +979,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="32" customWidth="1"/>
-    <col min="10" max="10" width="31" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="33" customWidth="1"/>
-    <col min="13" max="13" width="25" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="33" customWidth="1"/>
-    <col min="20" max="20" width="17" customWidth="1"/>
-    <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5">
-        <v>10000000</v>
-      </c>
-      <c r="C2" s="5">
-        <v>100000</v>
-      </c>
-      <c r="D2" s="5">
-        <v>50000</v>
-      </c>
-      <c r="E2" s="5">
-        <v>5000000</v>
-      </c>
-      <c r="F2" s="5">
-        <v>-50000</v>
-      </c>
-      <c r="G2" s="5">
-        <v>1500000</v>
-      </c>
-      <c r="H2" s="5">
-        <v>2000000</v>
-      </c>
-      <c r="I2" s="5">
-        <v>300000</v>
-      </c>
-      <c r="J2" s="5">
-        <v>50000</v>
-      </c>
-      <c r="K2" s="5">
-        <v>30000</v>
-      </c>
-      <c r="L2" s="5">
-        <v>20000</v>
-      </c>
-      <c r="M2" s="5">
-        <v>3500000</v>
-      </c>
-      <c r="N2" s="5">
-        <v>1500000</v>
-      </c>
-      <c r="O2" s="5">
-        <v>1200000</v>
-      </c>
-      <c r="P2" s="5">
-        <v>-200000</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>-350000</v>
-      </c>
-      <c r="R2" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="S2" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="T2" s="1"/>
-      <c r="U2" s="5">
-        <v>700000</v>
-      </c>
-      <c r="V2" s="6">
-        <v>-0.35</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:V2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"Aptos"&amp;9&amp;K000000 CLASSIFICAZIONE: INTERNO&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AP2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1184,127 +1027,127 @@
         <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AK1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AN1" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP1" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:42" ht="75" x14ac:dyDescent="0.25">
@@ -1318,22 +1161,22 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>0</v>
@@ -1351,55 +1194,55 @@
         <v>180</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="T2" s="6">
         <v>-0.18</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="Z2" s="6">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="AF2" s="1" t="b">
         <v>0</v>
@@ -1410,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="AK2" s="1" t="b">
         <v>1</v>
@@ -1421,25 +1264,203 @@
       <c r="AM2" s="1"/>
       <c r="AN2" s="1"/>
       <c r="AO2" s="1" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AP2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="R2" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="R2" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"GREEN,YELLOW,ORANGE,LIGHT_RED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="O2 P2" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="O2 P2" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Bonis,Past Due,Unlikely to Pay,Bad Loan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2 AF2 AK2 AL2" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2 AF2 AK2 AL2" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Aptos"&amp;9&amp;K000000 CLASSIFICAZIONE: INTERNO&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="33" customWidth="1"/>
+    <col min="13" max="13" width="25" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="17" customWidth="1"/>
+    <col min="19" max="19" width="33" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5">
+        <v>10000000</v>
+      </c>
+      <c r="C2" s="5">
+        <v>100000</v>
+      </c>
+      <c r="D2" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E2" s="5">
+        <v>5000000</v>
+      </c>
+      <c r="F2" s="5">
+        <v>-50000</v>
+      </c>
+      <c r="G2" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="I2" s="5">
+        <v>300000</v>
+      </c>
+      <c r="J2" s="5">
+        <v>50000</v>
+      </c>
+      <c r="K2" s="5">
+        <v>30000</v>
+      </c>
+      <c r="L2" s="5">
+        <v>20000</v>
+      </c>
+      <c r="M2" s="5">
+        <v>3500000</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="O2" s="5">
+        <v>1200000</v>
+      </c>
+      <c r="P2" s="5">
+        <v>-200000</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>-350000</v>
+      </c>
+      <c r="R2" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="S2" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="T2" s="1"/>
+      <c r="U2" s="5">
+        <v>700000</v>
+      </c>
+      <c r="V2" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="W2" s="6">
+        <v>4800000</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:V2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Aptos"&amp;9&amp;K000000 CLASSIFICAZIONE: INTERNO&amp;1#_x000D_</oddHeader>
@@ -1464,16 +1485,16 @@
         <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1519,16 +1540,16 @@
         <v>30</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{1D61D857-D16C-48DF-9DE9-6E87E719D52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Financial Analysis'!$A$1:$V$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D61D857-D16C-48DF-9DE9-6E87E719D52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548810F8-303B-4E9B-8AF1-8815CD168738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -23,14 +23,27 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Behavioural Analysis'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer Profile'!$A$1:$AP$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Debt Sustainability'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Financial Analysis'!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Financial Analysis'!$A$1:$W$2</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="124">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -399,6 +412,9 @@
   </si>
   <si>
     <t>debt_service</t>
+  </si>
+  <si>
+    <t>production_value</t>
   </si>
 </sst>
 </file>
@@ -1291,34 +1307,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="32" customWidth="1"/>
-    <col min="10" max="10" width="31" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="33" customWidth="1"/>
-    <col min="13" max="13" width="25" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="33" customWidth="1"/>
-    <col min="20" max="20" width="17" customWidth="1"/>
-    <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="18" customWidth="1"/>
-    <col min="23" max="23" width="24" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="32" customWidth="1"/>
+    <col min="11" max="11" width="31" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="33" customWidth="1"/>
+    <col min="14" max="14" width="25" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="33" customWidth="1"/>
+    <col min="21" max="21" width="17" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1332,64 +1348,67 @@
         <v>97</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1400,66 +1419,69 @@
         <v>100000</v>
       </c>
       <c r="D2" s="5">
+        <v>150000</v>
+      </c>
+      <c r="E2" s="5">
+        <v>150000</v>
+      </c>
+      <c r="F2" s="5">
+        <v>5000000</v>
+      </c>
+      <c r="G2" s="5">
+        <v>-50000</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1500000</v>
+      </c>
+      <c r="I2" s="5">
+        <v>2000000</v>
+      </c>
+      <c r="J2" s="5">
+        <v>300000</v>
+      </c>
+      <c r="K2" s="5">
         <v>50000</v>
       </c>
-      <c r="E2" s="5">
-        <v>5000000</v>
-      </c>
-      <c r="F2" s="5">
-        <v>-50000</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="L2" s="5">
+        <v>30000</v>
+      </c>
+      <c r="M2" s="5">
+        <v>20000</v>
+      </c>
+      <c r="N2" s="5">
+        <v>3500000</v>
+      </c>
+      <c r="O2" s="5">
         <v>1500000</v>
       </c>
-      <c r="H2" s="5">
-        <v>2000000</v>
-      </c>
-      <c r="I2" s="5">
-        <v>300000</v>
-      </c>
-      <c r="J2" s="5">
-        <v>50000</v>
-      </c>
-      <c r="K2" s="5">
-        <v>30000</v>
-      </c>
-      <c r="L2" s="5">
-        <v>20000</v>
-      </c>
-      <c r="M2" s="5">
-        <v>3500000</v>
-      </c>
-      <c r="N2" s="5">
-        <v>1500000</v>
-      </c>
-      <c r="O2" s="5">
+      <c r="P2" s="5">
         <v>1200000</v>
       </c>
-      <c r="P2" s="5">
+      <c r="Q2" s="5">
         <v>-200000</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="R2" s="5">
         <v>-350000</v>
       </c>
-      <c r="R2" s="6">
+      <c r="S2" s="6">
         <v>-0.1</v>
       </c>
-      <c r="S2" s="6">
+      <c r="T2" s="6">
         <v>0.01</v>
       </c>
-      <c r="T2" s="1"/>
-      <c r="U2" s="5">
+      <c r="U2" s="1"/>
+      <c r="V2" s="5">
         <v>700000</v>
       </c>
-      <c r="V2" s="6">
+      <c r="W2" s="6">
         <v>-0.35</v>
       </c>
-      <c r="W2" s="6">
+      <c r="X2" s="6">
         <v>4800000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:W2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Aptos"&amp;9&amp;K000000 CLASSIFICAZIONE: INTERNO&amp;1#_x000D_</oddHeader>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548810F8-303B-4E9B-8AF1-8815CD168738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FBCA95-D1B0-4FAB-B16B-142B84B44F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="129">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -415,6 +415,21 @@
   </si>
   <si>
     <t>production_value</t>
+  </si>
+  <si>
+    <t>bank_debt_current</t>
+  </si>
+  <si>
+    <t>bank_debt_1y_ago</t>
+  </si>
+  <si>
+    <t>bank_debt_2y_ago</t>
+  </si>
+  <si>
+    <t>bank_debt_3y_ago</t>
+  </si>
+  <si>
+    <t>bank_debt_4y_ago</t>
   </si>
 </sst>
 </file>
@@ -1307,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1332,9 +1347,14 @@
     <col min="22" max="22" width="20" customWidth="1"/>
     <col min="23" max="23" width="18" customWidth="1"/>
     <col min="24" max="24" width="24" customWidth="1"/>
+    <col min="25" max="25" width="21.7109375" customWidth="1"/>
+    <col min="26" max="26" width="19.7109375" customWidth="1"/>
+    <col min="27" max="27" width="25.5703125" customWidth="1"/>
+    <col min="28" max="28" width="26" customWidth="1"/>
+    <col min="29" max="29" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1407,8 +1427,23 @@
       <c r="X1" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+      <c r="Y1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1478,6 +1513,21 @@
       </c>
       <c r="X2" s="6">
         <v>4800000</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>800000</v>
       </c>
     </row>
   </sheetData>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FBCA95-D1B0-4FAB-B16B-142B84B44F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546646C9-65F5-482B-92E7-FA047E7B05DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="134">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -430,6 +430,21 @@
   </si>
   <si>
     <t>bank_debt_4y_ago</t>
+  </si>
+  <si>
+    <t>trade_payables_current</t>
+  </si>
+  <si>
+    <t>trade_payables_1y_ago</t>
+  </si>
+  <si>
+    <t>trade_payables_2y_ago</t>
+  </si>
+  <si>
+    <t>trade_payables_3y_ago</t>
+  </si>
+  <si>
+    <t>trade_payables_4y_ago</t>
   </si>
 </sst>
 </file>
@@ -1322,7 +1337,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1352,9 +1367,10 @@
     <col min="27" max="27" width="25.5703125" customWidth="1"/>
     <col min="28" max="28" width="26" customWidth="1"/>
     <col min="29" max="29" width="24" customWidth="1"/>
+    <col min="30" max="34" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1442,8 +1458,23 @@
       <c r="AC1" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="AD1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1527,6 +1558,21 @@
         <v>800000</v>
       </c>
       <c r="AC2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AH2" s="5">
         <v>800000</v>
       </c>
     </row>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546646C9-65F5-482B-92E7-FA047E7B05DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE56F73-8D2A-4A33-A8DF-C73F8296D09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="139">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -445,6 +445,21 @@
   </si>
   <si>
     <t>trade_payables_4y_ago</t>
+  </si>
+  <si>
+    <t>avg_payment_days_current</t>
+  </si>
+  <si>
+    <t>avg_payment_days_1y_ago</t>
+  </si>
+  <si>
+    <t>avg_payment_days_2y_ago</t>
+  </si>
+  <si>
+    <t>avg_payment_days_3y_ago</t>
+  </si>
+  <si>
+    <t>avg_payment_days_4y_ago</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AM2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1368,9 +1383,10 @@
     <col min="28" max="28" width="26" customWidth="1"/>
     <col min="29" max="29" width="24" customWidth="1"/>
     <col min="30" max="34" width="23" customWidth="1"/>
+    <col min="35" max="39" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1473,8 +1489,23 @@
       <c r="AH1" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" ht="45" x14ac:dyDescent="0.25">
+      <c r="AI1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1574,6 +1605,21 @@
       </c>
       <c r="AH2" s="5">
         <v>800000</v>
+      </c>
+      <c r="AI2" s="5">
+        <v>120</v>
+      </c>
+      <c r="AJ2" s="5">
+        <v>110</v>
+      </c>
+      <c r="AK2" s="5">
+        <v>90</v>
+      </c>
+      <c r="AL2" s="5">
+        <v>80</v>
+      </c>
+      <c r="AM2" s="5">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE56F73-8D2A-4A33-A8DF-C73F8296D09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D332B0A-ED21-4524-BBB1-64F8BE6720A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="141">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -460,6 +460,12 @@
   </si>
   <si>
     <t>avg_payment_days_4y_ago</t>
+  </si>
+  <si>
+    <t>tax_debt</t>
+  </si>
+  <si>
+    <t>total_liabilities</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1384,9 +1390,10 @@
     <col min="29" max="29" width="24" customWidth="1"/>
     <col min="30" max="34" width="23" customWidth="1"/>
     <col min="35" max="39" width="28.28515625" customWidth="1"/>
+    <col min="40" max="41" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1504,8 +1511,14 @@
       <c r="AM1" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="2" spans="1:39" ht="45" x14ac:dyDescent="0.25">
+      <c r="AN1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO1" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1620,6 +1633,12 @@
       </c>
       <c r="AM2" s="5">
         <v>70</v>
+      </c>
+      <c r="AN2" s="5">
+        <v>20000</v>
+      </c>
+      <c r="AO2" s="5">
+        <v>100000</v>
       </c>
     </row>
   </sheetData>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D332B0A-ED21-4524-BBB1-64F8BE6720A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7609DB-539C-4917-AB20-9222E62ABB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="146">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -466,6 +466,21 @@
   </si>
   <si>
     <t>total_liabilities</t>
+  </si>
+  <si>
+    <t>avg_collection_days_current</t>
+  </si>
+  <si>
+    <t>avg_collection_days_1y_ago</t>
+  </si>
+  <si>
+    <t>avg_collection_days_2y_ago</t>
+  </si>
+  <si>
+    <t>avg_collection_days_3y_ago</t>
+  </si>
+  <si>
+    <t>avg_collection_days_4y_ago</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AT2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1391,9 +1406,12 @@
     <col min="30" max="34" width="23" customWidth="1"/>
     <col min="35" max="39" width="28.28515625" customWidth="1"/>
     <col min="40" max="41" width="20.28515625" customWidth="1"/>
+    <col min="42" max="42" width="27.5703125" customWidth="1"/>
+    <col min="43" max="43" width="24.7109375" customWidth="1"/>
+    <col min="44" max="46" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1517,8 +1535,23 @@
       <c r="AO1" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="2" spans="1:41" ht="45" x14ac:dyDescent="0.25">
+      <c r="AP1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="AR1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1639,6 +1672,21 @@
       </c>
       <c r="AO2" s="5">
         <v>100000</v>
+      </c>
+      <c r="AP2" s="5">
+        <v>120</v>
+      </c>
+      <c r="AQ2" s="5">
+        <v>110</v>
+      </c>
+      <c r="AR2" s="5">
+        <v>90</v>
+      </c>
+      <c r="AS2" s="5">
+        <v>80</v>
+      </c>
+      <c r="AT2" s="5">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7609DB-539C-4917-AB20-9222E62ABB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FE07BA-425B-4F83-A034-4C7B27FFCD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Behavioural Analysis'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Customer Profile'!$A$1:$AP$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Debt Sustainability'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Financial Analysis'!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Financial Analysis'!$A$1:$X$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="149">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -481,6 +481,15 @@
   </si>
   <si>
     <t>avg_collection_days_4y_ago</t>
+  </si>
+  <si>
+    <t>revenue_1y_ago</t>
+  </si>
+  <si>
+    <t>trade_receivables_current</t>
+  </si>
+  <si>
+    <t>trade_receivables_1y_ago</t>
   </si>
 </sst>
 </file>
@@ -576,7 +585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -600,6 +609,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1373,45 +1385,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AW2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="8" width="34" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="32" customWidth="1"/>
-    <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="24" customWidth="1"/>
-    <col min="13" max="13" width="33" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
-    <col min="15" max="15" width="26" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="17" customWidth="1"/>
-    <col min="20" max="20" width="33" customWidth="1"/>
-    <col min="21" max="21" width="17" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="18" customWidth="1"/>
-    <col min="24" max="24" width="24" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" customWidth="1"/>
-    <col min="26" max="26" width="19.7109375" customWidth="1"/>
-    <col min="27" max="27" width="25.5703125" customWidth="1"/>
-    <col min="28" max="28" width="26" customWidth="1"/>
-    <col min="29" max="29" width="24" customWidth="1"/>
-    <col min="30" max="34" width="23" customWidth="1"/>
-    <col min="35" max="39" width="28.28515625" customWidth="1"/>
-    <col min="40" max="41" width="20.28515625" customWidth="1"/>
-    <col min="42" max="42" width="27.5703125" customWidth="1"/>
-    <col min="43" max="43" width="24.7109375" customWidth="1"/>
-    <col min="44" max="46" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="33" customWidth="1"/>
+    <col min="15" max="15" width="25" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="21" max="21" width="33" customWidth="1"/>
+    <col min="22" max="22" width="17" customWidth="1"/>
+    <col min="23" max="23" width="20" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="24" customWidth="1"/>
+    <col min="26" max="26" width="21.7109375" customWidth="1"/>
+    <col min="27" max="27" width="19.7109375" customWidth="1"/>
+    <col min="28" max="28" width="25.5703125" customWidth="1"/>
+    <col min="29" max="29" width="26" customWidth="1"/>
+    <col min="30" max="30" width="24" customWidth="1"/>
+    <col min="31" max="35" width="23" customWidth="1"/>
+    <col min="36" max="40" width="28.28515625" customWidth="1"/>
+    <col min="41" max="42" width="20.28515625" customWidth="1"/>
+    <col min="43" max="43" width="27.5703125" customWidth="1"/>
+    <col min="44" max="44" width="24.7109375" customWidth="1"/>
+    <col min="45" max="47" width="19.85546875" customWidth="1"/>
+    <col min="48" max="48" width="27.28515625" customWidth="1"/>
+    <col min="49" max="49" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1419,214 +1434,223 @@
         <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="2" spans="1:46" ht="45" x14ac:dyDescent="0.25">
+      <c r="AV1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AW1" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="9">
         <v>10000000</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="9">
+        <v>9000000</v>
+      </c>
+      <c r="D2" s="9">
         <v>100000</v>
       </c>
-      <c r="D2" s="5">
+      <c r="E2" s="9">
         <v>150000</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="9">
         <v>150000</v>
       </c>
-      <c r="F2" s="5">
+      <c r="G2" s="9">
         <v>5000000</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="9">
         <v>-50000</v>
       </c>
-      <c r="H2" s="5">
+      <c r="I2" s="9">
         <v>1500000</v>
       </c>
-      <c r="I2" s="5">
+      <c r="J2" s="9">
         <v>2000000</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="9">
         <v>300000</v>
       </c>
-      <c r="K2" s="5">
+      <c r="L2" s="9">
         <v>50000</v>
       </c>
-      <c r="L2" s="5">
+      <c r="M2" s="9">
         <v>30000</v>
       </c>
-      <c r="M2" s="5">
+      <c r="N2" s="9">
         <v>20000</v>
       </c>
-      <c r="N2" s="5">
+      <c r="O2" s="9">
         <v>3500000</v>
       </c>
-      <c r="O2" s="5">
+      <c r="P2" s="9">
         <v>1500000</v>
       </c>
-      <c r="P2" s="5">
+      <c r="Q2" s="9">
         <v>1200000</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="R2" s="9">
         <v>-200000</v>
       </c>
-      <c r="R2" s="5">
+      <c r="S2" s="9">
         <v>-350000</v>
       </c>
-      <c r="S2" s="6">
+      <c r="T2" s="9">
         <v>-0.1</v>
       </c>
-      <c r="T2" s="6">
+      <c r="U2" s="9">
         <v>0.01</v>
       </c>
-      <c r="U2" s="1"/>
-      <c r="V2" s="5">
+      <c r="V2" s="1"/>
+      <c r="W2" s="5">
         <v>700000</v>
       </c>
-      <c r="W2" s="6">
+      <c r="X2" s="6">
         <v>-0.35</v>
       </c>
-      <c r="X2" s="6">
+      <c r="Y2" s="6">
         <v>4800000</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="Z2" s="5">
         <v>1000000</v>
-      </c>
-      <c r="Z2" s="5">
-        <v>800000</v>
       </c>
       <c r="AA2" s="5">
         <v>800000</v>
@@ -1638,10 +1662,10 @@
         <v>800000</v>
       </c>
       <c r="AD2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AE2" s="5">
         <v>1000000</v>
-      </c>
-      <c r="AE2" s="5">
-        <v>800000</v>
       </c>
       <c r="AF2" s="5">
         <v>800000</v>
@@ -1653,44 +1677,53 @@
         <v>800000</v>
       </c>
       <c r="AI2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AJ2" s="5">
         <v>120</v>
       </c>
-      <c r="AJ2" s="5">
+      <c r="AK2" s="5">
         <v>110</v>
       </c>
-      <c r="AK2" s="5">
+      <c r="AL2" s="5">
         <v>90</v>
       </c>
-      <c r="AL2" s="5">
+      <c r="AM2" s="5">
         <v>80</v>
       </c>
-      <c r="AM2" s="5">
+      <c r="AN2" s="5">
         <v>70</v>
       </c>
-      <c r="AN2" s="5">
+      <c r="AO2" s="5">
         <v>20000</v>
       </c>
-      <c r="AO2" s="5">
+      <c r="AP2" s="5">
         <v>100000</v>
       </c>
-      <c r="AP2" s="5">
+      <c r="AQ2" s="5">
         <v>120</v>
       </c>
-      <c r="AQ2" s="5">
+      <c r="AR2" s="5">
         <v>110</v>
       </c>
-      <c r="AR2" s="5">
+      <c r="AS2" s="5">
         <v>90</v>
       </c>
-      <c r="AS2" s="5">
+      <c r="AT2" s="5">
         <v>80</v>
       </c>
-      <c r="AT2" s="5">
+      <c r="AU2" s="5">
         <v>70</v>
       </c>
+      <c r="AV2" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="AW2" s="5">
+        <v>800000</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:X2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Aptos"&amp;9&amp;K000000 CLASSIFICAZIONE: INTERNO&amp;1#_x000D_</oddHeader>

--- a/examples/excel/demo_scenarios.xlsx
+++ b/examples/excel/demo_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc1323\credit-assessment-system\examples\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FE07BA-425B-4F83-A034-4C7B27FFCD20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B732DA1F-F884-4DBC-8B91-3B000278E1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="151">
   <si>
     <t>Credit Assessment System — Integrated Demo Scenario</t>
   </si>
@@ -490,6 +490,12 @@
   </si>
   <si>
     <t>trade_receivables_1y_ago</t>
+  </si>
+  <si>
+    <t>intangible_assets</t>
+  </si>
+  <si>
+    <t>total_assets</t>
   </si>
 </sst>
 </file>
@@ -605,13 +611,13 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -922,10 +928,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1385,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1424,9 +1430,11 @@
     <col min="45" max="47" width="19.85546875" customWidth="1"/>
     <col min="48" max="48" width="27.28515625" customWidth="1"/>
     <col min="49" max="49" width="26.5703125" customWidth="1"/>
+    <col min="50" max="50" width="21.85546875" customWidth="1"/>
+    <col min="51" max="51" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1574,69 +1582,75 @@
       <c r="AW1" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="2" spans="1:49" ht="45" x14ac:dyDescent="0.25">
+      <c r="AX1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AY1" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="7">
         <v>10000000</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="7">
         <v>9000000</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="7">
         <v>100000</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="7">
         <v>150000</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="7">
         <v>150000</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="7">
         <v>5000000</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="7">
         <v>-50000</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="7">
         <v>1500000</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="7">
         <v>2000000</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="7">
         <v>300000</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="7">
         <v>50000</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="7">
         <v>30000</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="7">
         <v>20000</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="7">
         <v>3500000</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="7">
         <v>1500000</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="7">
         <v>1200000</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="7">
         <v>-200000</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="7">
         <v>-350000</v>
       </c>
-      <c r="T2" s="9">
+      <c r="T2" s="7">
         <v>-0.1</v>
       </c>
-      <c r="U2" s="9">
+      <c r="U2" s="7">
         <v>0.01</v>
       </c>
       <c r="V2" s="1"/>
@@ -1719,6 +1733,12 @@
         <v>1000000</v>
       </c>
       <c r="AW2" s="5">
+        <v>800000</v>
+      </c>
+      <c r="AX2" s="5">
+        <v>200000</v>
+      </c>
+      <c r="AY2" s="5">
         <v>800000</v>
       </c>
     </row>
